--- a/2024AIDataScienceGNRGeneral/Attendance.xlsx
+++ b/2024AIDataScienceGNRGeneral/Attendance.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\Batches\2024AIDataScienceGNRGeneral\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\2024AIDataScienceGNRGeneral\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE6CFE45-7ADB-45E6-BAB3-C6AA53E5003A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B78D06A-82F0-421C-B4F8-1575A5249199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="26">
   <si>
     <t>Name</t>
   </si>
@@ -421,7 +421,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.21875" bestFit="1" customWidth="1"/>
@@ -433,7 +433,7 @@
     <col min="10" max="10" width="6.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -470,8 +470,11 @@
       <c r="M1" s="1">
         <v>45577</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N1" s="1">
+        <v>45584</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -511,8 +514,11 @@
       <c r="M2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -552,8 +558,11 @@
       <c r="M3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -593,8 +602,11 @@
       <c r="M4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -634,8 +646,11 @@
       <c r="M5" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -675,8 +690,11 @@
       <c r="M6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -716,8 +734,11 @@
       <c r="M7" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -757,8 +778,11 @@
       <c r="M8" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -798,8 +822,11 @@
       <c r="M9" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -839,8 +866,11 @@
       <c r="M10" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -880,8 +910,11 @@
       <c r="M11" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -921,8 +954,11 @@
       <c r="M12" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -962,8 +998,11 @@
       <c r="M13" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>6</v>
       </c>
@@ -1003,8 +1042,11 @@
       <c r="M14" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>7</v>
       </c>
@@ -1044,8 +1086,11 @@
       <c r="M15" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -1085,8 +1130,11 @@
       <c r="M16" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>14</v>
       </c>
@@ -1126,8 +1174,11 @@
       <c r="M17" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -1165,6 +1216,9 @@
         <v>21</v>
       </c>
       <c r="M18" t="s">
+        <v>21</v>
+      </c>
+      <c r="N18" t="s">
         <v>21</v>
       </c>
     </row>

--- a/2024AIDataScienceGNRGeneral/Attendance.xlsx
+++ b/2024AIDataScienceGNRGeneral/Attendance.xlsx
@@ -8,14 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\2024AIDataScienceGNRGeneral\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B78D06A-82F0-421C-B4F8-1575A5249199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D4533F5-2184-4223-8158-B23AAD79695B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Local Students" sheetId="2" r:id="rId2"/>
+    <sheet name="Local Students Score Card" sheetId="4" r:id="rId3"/>
+    <sheet name="Outsider Students" sheetId="3" r:id="rId4"/>
+    <sheet name="Outsider Students Score Card" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="28">
   <si>
     <t>Name</t>
   </si>
@@ -103,6 +107,12 @@
   </si>
   <si>
     <t>Shreya Thakkar</t>
+  </si>
+  <si>
+    <t>Attendance/60</t>
+  </si>
+  <si>
+    <t>Attendance/5</t>
   </si>
 </sst>
 </file>
@@ -1228,4 +1238,2079 @@
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2E48AE9-F3B8-426E-86DC-7F1D25270B25}">
+  <dimension ref="A1:N15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1">
+        <v>45500</v>
+      </c>
+      <c r="D1" s="1">
+        <v>45507</v>
+      </c>
+      <c r="E1" s="1">
+        <v>45514</v>
+      </c>
+      <c r="F1" s="1">
+        <v>45521</v>
+      </c>
+      <c r="G1" s="1">
+        <v>45528</v>
+      </c>
+      <c r="H1" s="1">
+        <v>45535</v>
+      </c>
+      <c r="I1" s="1">
+        <v>45542</v>
+      </c>
+      <c r="J1" s="1">
+        <v>45549</v>
+      </c>
+      <c r="K1" s="1">
+        <v>45565</v>
+      </c>
+      <c r="L1" s="1">
+        <v>45572</v>
+      </c>
+      <c r="M1" s="1">
+        <v>45577</v>
+      </c>
+      <c r="N1" s="1">
+        <v>45584</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" t="s">
+        <v>9</v>
+      </c>
+      <c r="N2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4" t="s">
+        <v>9</v>
+      </c>
+      <c r="K4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M4" t="s">
+        <v>21</v>
+      </c>
+      <c r="N4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" t="s">
+        <v>9</v>
+      </c>
+      <c r="K5" t="s">
+        <v>21</v>
+      </c>
+      <c r="L5" t="s">
+        <v>15</v>
+      </c>
+      <c r="M5" t="s">
+        <v>9</v>
+      </c>
+      <c r="N5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" t="s">
+        <v>9</v>
+      </c>
+      <c r="J6" t="s">
+        <v>9</v>
+      </c>
+      <c r="K6" t="s">
+        <v>15</v>
+      </c>
+      <c r="L6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M6" t="s">
+        <v>21</v>
+      </c>
+      <c r="N6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" t="s">
+        <v>9</v>
+      </c>
+      <c r="I7" t="s">
+        <v>9</v>
+      </c>
+      <c r="J7" t="s">
+        <v>9</v>
+      </c>
+      <c r="K7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7" t="s">
+        <v>15</v>
+      </c>
+      <c r="M7" t="s">
+        <v>9</v>
+      </c>
+      <c r="N7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G8" t="s">
+        <v>9</v>
+      </c>
+      <c r="H8" t="s">
+        <v>9</v>
+      </c>
+      <c r="I8" t="s">
+        <v>9</v>
+      </c>
+      <c r="J8" t="s">
+        <v>9</v>
+      </c>
+      <c r="K8" t="s">
+        <v>21</v>
+      </c>
+      <c r="L8" t="s">
+        <v>15</v>
+      </c>
+      <c r="M8" t="s">
+        <v>9</v>
+      </c>
+      <c r="N8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9" t="s">
+        <v>9</v>
+      </c>
+      <c r="H9" t="s">
+        <v>9</v>
+      </c>
+      <c r="I9" t="s">
+        <v>9</v>
+      </c>
+      <c r="J9" t="s">
+        <v>9</v>
+      </c>
+      <c r="K9" t="s">
+        <v>9</v>
+      </c>
+      <c r="L9" t="s">
+        <v>15</v>
+      </c>
+      <c r="M9" t="s">
+        <v>9</v>
+      </c>
+      <c r="N9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G10" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" t="s">
+        <v>9</v>
+      </c>
+      <c r="I10" t="s">
+        <v>9</v>
+      </c>
+      <c r="J10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K10" t="s">
+        <v>9</v>
+      </c>
+      <c r="L10" t="s">
+        <v>15</v>
+      </c>
+      <c r="M10" t="s">
+        <v>9</v>
+      </c>
+      <c r="N10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G11" t="s">
+        <v>21</v>
+      </c>
+      <c r="H11" t="s">
+        <v>9</v>
+      </c>
+      <c r="I11" t="s">
+        <v>9</v>
+      </c>
+      <c r="J11" t="s">
+        <v>9</v>
+      </c>
+      <c r="K11" t="s">
+        <v>9</v>
+      </c>
+      <c r="L11" t="s">
+        <v>15</v>
+      </c>
+      <c r="M11" t="s">
+        <v>9</v>
+      </c>
+      <c r="N11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G12" t="s">
+        <v>9</v>
+      </c>
+      <c r="H12" t="s">
+        <v>9</v>
+      </c>
+      <c r="I12" t="s">
+        <v>21</v>
+      </c>
+      <c r="J12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K12" t="s">
+        <v>15</v>
+      </c>
+      <c r="L12" t="s">
+        <v>21</v>
+      </c>
+      <c r="M12" t="s">
+        <v>15</v>
+      </c>
+      <c r="N12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" t="s">
+        <v>9</v>
+      </c>
+      <c r="G13" t="s">
+        <v>9</v>
+      </c>
+      <c r="H13" t="s">
+        <v>9</v>
+      </c>
+      <c r="I13" t="s">
+        <v>9</v>
+      </c>
+      <c r="J13" t="s">
+        <v>21</v>
+      </c>
+      <c r="K13" t="s">
+        <v>15</v>
+      </c>
+      <c r="L13" t="s">
+        <v>15</v>
+      </c>
+      <c r="M13" t="s">
+        <v>15</v>
+      </c>
+      <c r="N13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" t="s">
+        <v>21</v>
+      </c>
+      <c r="E14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" t="s">
+        <v>21</v>
+      </c>
+      <c r="G14" t="s">
+        <v>21</v>
+      </c>
+      <c r="H14" t="s">
+        <v>21</v>
+      </c>
+      <c r="I14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J14" t="s">
+        <v>21</v>
+      </c>
+      <c r="K14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L14" t="s">
+        <v>21</v>
+      </c>
+      <c r="M14" t="s">
+        <v>21</v>
+      </c>
+      <c r="N14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" t="s">
+        <v>9</v>
+      </c>
+      <c r="G15" t="s">
+        <v>9</v>
+      </c>
+      <c r="H15" t="s">
+        <v>9</v>
+      </c>
+      <c r="I15" t="s">
+        <v>21</v>
+      </c>
+      <c r="J15" t="s">
+        <v>21</v>
+      </c>
+      <c r="K15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L15" t="s">
+        <v>21</v>
+      </c>
+      <c r="M15" t="s">
+        <v>21</v>
+      </c>
+      <c r="N15" t="s">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44A055E7-9255-48F8-A415-3901F2D95410}">
+  <dimension ref="A1:P15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="15" max="15" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1">
+        <v>45500</v>
+      </c>
+      <c r="D1" s="1">
+        <v>45507</v>
+      </c>
+      <c r="E1" s="1">
+        <v>45514</v>
+      </c>
+      <c r="F1" s="1">
+        <v>45521</v>
+      </c>
+      <c r="G1" s="1">
+        <v>45528</v>
+      </c>
+      <c r="H1" s="1">
+        <v>45535</v>
+      </c>
+      <c r="I1" s="1">
+        <v>45542</v>
+      </c>
+      <c r="J1" s="1">
+        <v>45549</v>
+      </c>
+      <c r="K1" s="1">
+        <v>45565</v>
+      </c>
+      <c r="L1" s="1">
+        <v>45572</v>
+      </c>
+      <c r="M1" s="1">
+        <v>45577</v>
+      </c>
+      <c r="N1" s="1">
+        <v>45584</v>
+      </c>
+      <c r="O1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2">
+        <f>_xlfn.IFS('Local Students'!C2="P",5,'Local Students'!C2="O",3,'Local Students'!C2="A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <f>_xlfn.IFS('Local Students'!D2="P",5,'Local Students'!D2="O",3,'Local Students'!D2="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <f>_xlfn.IFS('Local Students'!E2="P",5,'Local Students'!E2="O",3,'Local Students'!E2="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <f>_xlfn.IFS('Local Students'!F2="P",5,'Local Students'!F2="O",3,'Local Students'!F2="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <f>_xlfn.IFS('Local Students'!G2="P",5,'Local Students'!G2="O",3,'Local Students'!G2="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="H2">
+        <f>_xlfn.IFS('Local Students'!H2="P",5,'Local Students'!H2="O",3,'Local Students'!H2="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <f>_xlfn.IFS('Local Students'!I2="P",5,'Local Students'!I2="O",3,'Local Students'!I2="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="J2">
+        <f>_xlfn.IFS('Local Students'!J2="P",5,'Local Students'!J2="O",3,'Local Students'!J2="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="K2">
+        <f>_xlfn.IFS('Local Students'!K2="P",5,'Local Students'!K2="O",3,'Local Students'!K2="A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="L2">
+        <f>_xlfn.IFS('Local Students'!L2="P",5,'Local Students'!L2="O",3,'Local Students'!L2="A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="M2">
+        <f>_xlfn.IFS('Local Students'!M2="P",5,'Local Students'!M2="O",3,'Local Students'!M2="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="N2">
+        <f>_xlfn.IFS('Local Students'!N2="P",5,'Local Students'!N2="O",3,'Local Students'!N2="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="O2">
+        <f>SUM(C2:N2)</f>
+        <v>49</v>
+      </c>
+      <c r="P2">
+        <f>ROUND(O2*5/60, 2)</f>
+        <v>4.08</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3">
+        <f>_xlfn.IFS('Local Students'!C3="P",5,'Local Students'!C3="O",3,'Local Students'!C3="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <f>_xlfn.IFS('Local Students'!D3="P",5,'Local Students'!D3="O",3,'Local Students'!D3="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <f>_xlfn.IFS('Local Students'!E3="P",5,'Local Students'!E3="O",3,'Local Students'!E3="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="F3">
+        <f>_xlfn.IFS('Local Students'!F3="P",5,'Local Students'!F3="O",3,'Local Students'!F3="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="G3">
+        <f>_xlfn.IFS('Local Students'!G3="P",5,'Local Students'!G3="O",3,'Local Students'!G3="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="H3">
+        <f>_xlfn.IFS('Local Students'!H3="P",5,'Local Students'!H3="O",3,'Local Students'!H3="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="I3">
+        <f>_xlfn.IFS('Local Students'!I3="P",5,'Local Students'!I3="O",3,'Local Students'!I3="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="J3">
+        <f>_xlfn.IFS('Local Students'!J3="P",5,'Local Students'!J3="O",3,'Local Students'!J3="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="K3">
+        <f>_xlfn.IFS('Local Students'!K3="P",5,'Local Students'!K3="O",3,'Local Students'!K3="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <f>_xlfn.IFS('Local Students'!L3="P",5,'Local Students'!L3="O",3,'Local Students'!L3="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <f>_xlfn.IFS('Local Students'!M3="P",5,'Local Students'!M3="O",3,'Local Students'!M3="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <f>_xlfn.IFS('Local Students'!N3="P",5,'Local Students'!N3="O",3,'Local Students'!N3="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <f t="shared" ref="O3:O15" si="0">SUM(C3:N3)</f>
+        <v>40</v>
+      </c>
+      <c r="P3">
+        <f t="shared" ref="P3:P15" si="1">ROUND(O3*5/60, 2)</f>
+        <v>3.33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4">
+        <f>_xlfn.IFS('Local Students'!C4="P",5,'Local Students'!C4="O",3,'Local Students'!C4="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="D4">
+        <f>_xlfn.IFS('Local Students'!D4="P",5,'Local Students'!D4="O",3,'Local Students'!D4="A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <f>_xlfn.IFS('Local Students'!E4="P",5,'Local Students'!E4="O",3,'Local Students'!E4="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <f>_xlfn.IFS('Local Students'!F4="P",5,'Local Students'!F4="O",3,'Local Students'!F4="A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="G4">
+        <f>_xlfn.IFS('Local Students'!G4="P",5,'Local Students'!G4="O",3,'Local Students'!G4="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <f>_xlfn.IFS('Local Students'!H4="P",5,'Local Students'!H4="O",3,'Local Students'!H4="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <f>_xlfn.IFS('Local Students'!I4="P",5,'Local Students'!I4="O",3,'Local Students'!I4="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <f>_xlfn.IFS('Local Students'!J4="P",5,'Local Students'!J4="O",3,'Local Students'!J4="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="K4">
+        <f>_xlfn.IFS('Local Students'!K4="P",5,'Local Students'!K4="O",3,'Local Students'!K4="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <f>_xlfn.IFS('Local Students'!L4="P",5,'Local Students'!L4="O",3,'Local Students'!L4="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <f>_xlfn.IFS('Local Students'!M4="P",5,'Local Students'!M4="O",3,'Local Students'!M4="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <f>_xlfn.IFS('Local Students'!N4="P",5,'Local Students'!N4="O",3,'Local Students'!N4="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="O4">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="P4">
+        <f t="shared" si="1"/>
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5">
+        <f>_xlfn.IFS('Local Students'!C5="P",5,'Local Students'!C5="O",3,'Local Students'!C5="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <f>_xlfn.IFS('Local Students'!D5="P",5,'Local Students'!D5="O",3,'Local Students'!D5="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <f>_xlfn.IFS('Local Students'!E5="P",5,'Local Students'!E5="O",3,'Local Students'!E5="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <f>_xlfn.IFS('Local Students'!F5="P",5,'Local Students'!F5="O",3,'Local Students'!F5="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="G5">
+        <f>_xlfn.IFS('Local Students'!G5="P",5,'Local Students'!G5="O",3,'Local Students'!G5="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="H5">
+        <f>_xlfn.IFS('Local Students'!H5="P",5,'Local Students'!H5="O",3,'Local Students'!H5="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="I5">
+        <f>_xlfn.IFS('Local Students'!I5="P",5,'Local Students'!I5="O",3,'Local Students'!I5="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="J5">
+        <f>_xlfn.IFS('Local Students'!J5="P",5,'Local Students'!J5="O",3,'Local Students'!J5="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <f>_xlfn.IFS('Local Students'!K5="P",5,'Local Students'!K5="O",3,'Local Students'!K5="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <f>_xlfn.IFS('Local Students'!L5="P",5,'Local Students'!L5="O",3,'Local Students'!L5="A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="M5">
+        <f>_xlfn.IFS('Local Students'!M5="P",5,'Local Students'!M5="O",3,'Local Students'!M5="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="N5">
+        <f>_xlfn.IFS('Local Students'!N5="P",5,'Local Students'!N5="O",3,'Local Students'!N5="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="O5">
+        <f t="shared" si="0"/>
+        <v>53</v>
+      </c>
+      <c r="P5">
+        <f t="shared" si="1"/>
+        <v>4.42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6">
+        <f>_xlfn.IFS('Local Students'!C6="P",5,'Local Students'!C6="O",3,'Local Students'!C6="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <f>_xlfn.IFS('Local Students'!D6="P",5,'Local Students'!D6="O",3,'Local Students'!D6="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <f>_xlfn.IFS('Local Students'!E6="P",5,'Local Students'!E6="O",3,'Local Students'!E6="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <f>_xlfn.IFS('Local Students'!F6="P",5,'Local Students'!F6="O",3,'Local Students'!F6="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="G6">
+        <f>_xlfn.IFS('Local Students'!G6="P",5,'Local Students'!G6="O",3,'Local Students'!G6="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <f>_xlfn.IFS('Local Students'!H6="P",5,'Local Students'!H6="O",3,'Local Students'!H6="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="I6">
+        <f>_xlfn.IFS('Local Students'!I6="P",5,'Local Students'!I6="O",3,'Local Students'!I6="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="J6">
+        <f>_xlfn.IFS('Local Students'!J6="P",5,'Local Students'!J6="O",3,'Local Students'!J6="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <f>_xlfn.IFS('Local Students'!K6="P",5,'Local Students'!K6="O",3,'Local Students'!K6="A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="L6">
+        <f>_xlfn.IFS('Local Students'!L6="P",5,'Local Students'!L6="O",3,'Local Students'!L6="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <f>_xlfn.IFS('Local Students'!M6="P",5,'Local Students'!M6="O",3,'Local Students'!M6="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <f>_xlfn.IFS('Local Students'!N6="P",5,'Local Students'!N6="O",3,'Local Students'!N6="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="O6">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="P6">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7">
+        <f>_xlfn.IFS('Local Students'!C7="P",5,'Local Students'!C7="O",3,'Local Students'!C7="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="D7">
+        <f>_xlfn.IFS('Local Students'!D7="P",5,'Local Students'!D7="O",3,'Local Students'!D7="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="E7">
+        <f>_xlfn.IFS('Local Students'!E7="P",5,'Local Students'!E7="O",3,'Local Students'!E7="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="F7">
+        <f>_xlfn.IFS('Local Students'!F7="P",5,'Local Students'!F7="O",3,'Local Students'!F7="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="G7">
+        <f>_xlfn.IFS('Local Students'!G7="P",5,'Local Students'!G7="O",3,'Local Students'!G7="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="H7">
+        <f>_xlfn.IFS('Local Students'!H7="P",5,'Local Students'!H7="O",3,'Local Students'!H7="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="I7">
+        <f>_xlfn.IFS('Local Students'!I7="P",5,'Local Students'!I7="O",3,'Local Students'!I7="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="J7">
+        <f>_xlfn.IFS('Local Students'!J7="P",5,'Local Students'!J7="O",3,'Local Students'!J7="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="K7">
+        <f>_xlfn.IFS('Local Students'!K7="P",5,'Local Students'!K7="O",3,'Local Students'!K7="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <f>_xlfn.IFS('Local Students'!L7="P",5,'Local Students'!L7="O",3,'Local Students'!L7="A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="M7">
+        <f>_xlfn.IFS('Local Students'!M7="P",5,'Local Students'!M7="O",3,'Local Students'!M7="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="N7">
+        <f>_xlfn.IFS('Local Students'!N7="P",5,'Local Students'!N7="O",3,'Local Students'!N7="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="O7">
+        <f t="shared" si="0"/>
+        <v>53</v>
+      </c>
+      <c r="P7">
+        <f t="shared" si="1"/>
+        <v>4.42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8">
+        <f>_xlfn.IFS('Local Students'!C8="P",5,'Local Students'!C8="O",3,'Local Students'!C8="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <f>_xlfn.IFS('Local Students'!D8="P",5,'Local Students'!D8="O",3,'Local Students'!D8="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <f>_xlfn.IFS('Local Students'!E8="P",5,'Local Students'!E8="O",3,'Local Students'!E8="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="F8">
+        <f>_xlfn.IFS('Local Students'!F8="P",5,'Local Students'!F8="O",3,'Local Students'!F8="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="G8">
+        <f>_xlfn.IFS('Local Students'!G8="P",5,'Local Students'!G8="O",3,'Local Students'!G8="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="H8">
+        <f>_xlfn.IFS('Local Students'!H8="P",5,'Local Students'!H8="O",3,'Local Students'!H8="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="I8">
+        <f>_xlfn.IFS('Local Students'!I8="P",5,'Local Students'!I8="O",3,'Local Students'!I8="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="J8">
+        <f>_xlfn.IFS('Local Students'!J8="P",5,'Local Students'!J8="O",3,'Local Students'!J8="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="K8">
+        <f>_xlfn.IFS('Local Students'!K8="P",5,'Local Students'!K8="O",3,'Local Students'!K8="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <f>_xlfn.IFS('Local Students'!L8="P",5,'Local Students'!L8="O",3,'Local Students'!L8="A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="M8">
+        <f>_xlfn.IFS('Local Students'!M8="P",5,'Local Students'!M8="O",3,'Local Students'!M8="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="N8">
+        <f>_xlfn.IFS('Local Students'!N8="P",5,'Local Students'!N8="O",3,'Local Students'!N8="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="O8">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="P8">
+        <f t="shared" si="1"/>
+        <v>3.58</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9">
+        <f>_xlfn.IFS('Local Students'!C9="P",5,'Local Students'!C9="O",3,'Local Students'!C9="A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="D9">
+        <f>_xlfn.IFS('Local Students'!D9="P",5,'Local Students'!D9="O",3,'Local Students'!D9="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="E9">
+        <f>_xlfn.IFS('Local Students'!E9="P",5,'Local Students'!E9="O",3,'Local Students'!E9="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="F9">
+        <f>_xlfn.IFS('Local Students'!F9="P",5,'Local Students'!F9="O",3,'Local Students'!F9="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="G9">
+        <f>_xlfn.IFS('Local Students'!G9="P",5,'Local Students'!G9="O",3,'Local Students'!G9="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="H9">
+        <f>_xlfn.IFS('Local Students'!H9="P",5,'Local Students'!H9="O",3,'Local Students'!H9="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="I9">
+        <f>_xlfn.IFS('Local Students'!I9="P",5,'Local Students'!I9="O",3,'Local Students'!I9="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="J9">
+        <f>_xlfn.IFS('Local Students'!J9="P",5,'Local Students'!J9="O",3,'Local Students'!J9="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="K9">
+        <f>_xlfn.IFS('Local Students'!K9="P",5,'Local Students'!K9="O",3,'Local Students'!K9="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="L9">
+        <f>_xlfn.IFS('Local Students'!L9="P",5,'Local Students'!L9="O",3,'Local Students'!L9="A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="M9">
+        <f>_xlfn.IFS('Local Students'!M9="P",5,'Local Students'!M9="O",3,'Local Students'!M9="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="N9">
+        <f>_xlfn.IFS('Local Students'!N9="P",5,'Local Students'!N9="O",3,'Local Students'!N9="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="O9">
+        <f t="shared" si="0"/>
+        <v>56</v>
+      </c>
+      <c r="P9">
+        <f t="shared" si="1"/>
+        <v>4.67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10">
+        <f>_xlfn.IFS('Local Students'!C10="P",5,'Local Students'!C10="O",3,'Local Students'!C10="A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="D10">
+        <f>_xlfn.IFS('Local Students'!D10="P",5,'Local Students'!D10="O",3,'Local Students'!D10="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="E10">
+        <f>_xlfn.IFS('Local Students'!E10="P",5,'Local Students'!E10="O",3,'Local Students'!E10="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="F10">
+        <f>_xlfn.IFS('Local Students'!F10="P",5,'Local Students'!F10="O",3,'Local Students'!F10="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="G10">
+        <f>_xlfn.IFS('Local Students'!G10="P",5,'Local Students'!G10="O",3,'Local Students'!G10="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="H10">
+        <f>_xlfn.IFS('Local Students'!H10="P",5,'Local Students'!H10="O",3,'Local Students'!H10="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="I10">
+        <f>_xlfn.IFS('Local Students'!I10="P",5,'Local Students'!I10="O",3,'Local Students'!I10="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="J10">
+        <f>_xlfn.IFS('Local Students'!J10="P",5,'Local Students'!J10="O",3,'Local Students'!J10="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <f>_xlfn.IFS('Local Students'!K10="P",5,'Local Students'!K10="O",3,'Local Students'!K10="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="L10">
+        <f>_xlfn.IFS('Local Students'!L10="P",5,'Local Students'!L10="O",3,'Local Students'!L10="A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="M10">
+        <f>_xlfn.IFS('Local Students'!M10="P",5,'Local Students'!M10="O",3,'Local Students'!M10="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="N10">
+        <f>_xlfn.IFS('Local Students'!N10="P",5,'Local Students'!N10="O",3,'Local Students'!N10="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="O10">
+        <f t="shared" si="0"/>
+        <v>51</v>
+      </c>
+      <c r="P10">
+        <f t="shared" si="1"/>
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11">
+        <f>_xlfn.IFS('Local Students'!C11="P",5,'Local Students'!C11="O",3,'Local Students'!C11="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="D11">
+        <f>_xlfn.IFS('Local Students'!D11="P",5,'Local Students'!D11="O",3,'Local Students'!D11="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="E11">
+        <f>_xlfn.IFS('Local Students'!E11="P",5,'Local Students'!E11="O",3,'Local Students'!E11="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="F11">
+        <f>_xlfn.IFS('Local Students'!F11="P",5,'Local Students'!F11="O",3,'Local Students'!F11="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="G11">
+        <f>_xlfn.IFS('Local Students'!G11="P",5,'Local Students'!G11="O",3,'Local Students'!G11="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <f>_xlfn.IFS('Local Students'!H11="P",5,'Local Students'!H11="O",3,'Local Students'!H11="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="I11">
+        <f>_xlfn.IFS('Local Students'!I11="P",5,'Local Students'!I11="O",3,'Local Students'!I11="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="J11">
+        <f>_xlfn.IFS('Local Students'!J11="P",5,'Local Students'!J11="O",3,'Local Students'!J11="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="K11">
+        <f>_xlfn.IFS('Local Students'!K11="P",5,'Local Students'!K11="O",3,'Local Students'!K11="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="L11">
+        <f>_xlfn.IFS('Local Students'!L11="P",5,'Local Students'!L11="O",3,'Local Students'!L11="A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="M11">
+        <f>_xlfn.IFS('Local Students'!M11="P",5,'Local Students'!M11="O",3,'Local Students'!M11="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="N11">
+        <f>_xlfn.IFS('Local Students'!N11="P",5,'Local Students'!N11="O",3,'Local Students'!N11="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="O11">
+        <f t="shared" si="0"/>
+        <v>53</v>
+      </c>
+      <c r="P11">
+        <f t="shared" si="1"/>
+        <v>4.42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12">
+        <f>_xlfn.IFS('Local Students'!C12="P",5,'Local Students'!C12="O",3,'Local Students'!C12="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="D12">
+        <f>_xlfn.IFS('Local Students'!D12="P",5,'Local Students'!D12="O",3,'Local Students'!D12="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="E12">
+        <f>_xlfn.IFS('Local Students'!E12="P",5,'Local Students'!E12="O",3,'Local Students'!E12="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="F12">
+        <f>_xlfn.IFS('Local Students'!F12="P",5,'Local Students'!F12="O",3,'Local Students'!F12="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <f>_xlfn.IFS('Local Students'!G12="P",5,'Local Students'!G12="O",3,'Local Students'!G12="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="H12">
+        <f>_xlfn.IFS('Local Students'!H12="P",5,'Local Students'!H12="O",3,'Local Students'!H12="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="I12">
+        <f>_xlfn.IFS('Local Students'!I12="P",5,'Local Students'!I12="O",3,'Local Students'!I12="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <f>_xlfn.IFS('Local Students'!J12="P",5,'Local Students'!J12="O",3,'Local Students'!J12="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <f>_xlfn.IFS('Local Students'!K12="P",5,'Local Students'!K12="O",3,'Local Students'!K12="A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="L12">
+        <f>_xlfn.IFS('Local Students'!L12="P",5,'Local Students'!L12="O",3,'Local Students'!L12="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <f>_xlfn.IFS('Local Students'!M12="P",5,'Local Students'!M12="O",3,'Local Students'!M12="A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="N12">
+        <f>_xlfn.IFS('Local Students'!N12="P",5,'Local Students'!N12="O",3,'Local Students'!N12="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="O12">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="P12">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13">
+        <f>_xlfn.IFS('Local Students'!C13="P",5,'Local Students'!C13="O",3,'Local Students'!C13="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="D13">
+        <f>_xlfn.IFS('Local Students'!D13="P",5,'Local Students'!D13="O",3,'Local Students'!D13="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="E13">
+        <f>_xlfn.IFS('Local Students'!E13="P",5,'Local Students'!E13="O",3,'Local Students'!E13="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="F13">
+        <f>_xlfn.IFS('Local Students'!F13="P",5,'Local Students'!F13="O",3,'Local Students'!F13="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="G13">
+        <f>_xlfn.IFS('Local Students'!G13="P",5,'Local Students'!G13="O",3,'Local Students'!G13="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="H13">
+        <f>_xlfn.IFS('Local Students'!H13="P",5,'Local Students'!H13="O",3,'Local Students'!H13="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="I13">
+        <f>_xlfn.IFS('Local Students'!I13="P",5,'Local Students'!I13="O",3,'Local Students'!I13="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="J13">
+        <f>_xlfn.IFS('Local Students'!J13="P",5,'Local Students'!J13="O",3,'Local Students'!J13="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <f>_xlfn.IFS('Local Students'!K13="P",5,'Local Students'!K13="O",3,'Local Students'!K13="A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="L13">
+        <f>_xlfn.IFS('Local Students'!L13="P",5,'Local Students'!L13="O",3,'Local Students'!L13="A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="M13">
+        <f>_xlfn.IFS('Local Students'!M13="P",5,'Local Students'!M13="O",3,'Local Students'!M13="A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="N13">
+        <f>_xlfn.IFS('Local Students'!N13="P",5,'Local Students'!N13="O",3,'Local Students'!N13="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="O13">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+      <c r="P13">
+        <f t="shared" si="1"/>
+        <v>4.08</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14">
+        <f>_xlfn.IFS('Local Students'!C14="P",5,'Local Students'!C14="O",3,'Local Students'!C14="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <f>_xlfn.IFS('Local Students'!D14="P",5,'Local Students'!D14="O",3,'Local Students'!D14="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <f>_xlfn.IFS('Local Students'!E14="P",5,'Local Students'!E14="O",3,'Local Students'!E14="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="F14">
+        <f>_xlfn.IFS('Local Students'!F14="P",5,'Local Students'!F14="O",3,'Local Students'!F14="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <f>_xlfn.IFS('Local Students'!G14="P",5,'Local Students'!G14="O",3,'Local Students'!G14="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <f>_xlfn.IFS('Local Students'!H14="P",5,'Local Students'!H14="O",3,'Local Students'!H14="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <f>_xlfn.IFS('Local Students'!I14="P",5,'Local Students'!I14="O",3,'Local Students'!I14="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <f>_xlfn.IFS('Local Students'!J14="P",5,'Local Students'!J14="O",3,'Local Students'!J14="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <f>_xlfn.IFS('Local Students'!K14="P",5,'Local Students'!K14="O",3,'Local Students'!K14="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <f>_xlfn.IFS('Local Students'!L14="P",5,'Local Students'!L14="O",3,'Local Students'!L14="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <f>_xlfn.IFS('Local Students'!M14="P",5,'Local Students'!M14="O",3,'Local Students'!M14="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <f>_xlfn.IFS('Local Students'!N14="P",5,'Local Students'!N14="O",3,'Local Students'!N14="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="P14">
+        <f t="shared" si="1"/>
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15">
+        <f>_xlfn.IFS('Local Students'!C15="P",5,'Local Students'!C15="O",3,'Local Students'!C15="A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="D15">
+        <f>_xlfn.IFS('Local Students'!D15="P",5,'Local Students'!D15="O",3,'Local Students'!D15="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="E15">
+        <f>_xlfn.IFS('Local Students'!E15="P",5,'Local Students'!E15="O",3,'Local Students'!E15="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="F15">
+        <f>_xlfn.IFS('Local Students'!F15="P",5,'Local Students'!F15="O",3,'Local Students'!F15="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="G15">
+        <f>_xlfn.IFS('Local Students'!G15="P",5,'Local Students'!G15="O",3,'Local Students'!G15="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="H15">
+        <f>_xlfn.IFS('Local Students'!H15="P",5,'Local Students'!H15="O",3,'Local Students'!H15="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="I15">
+        <f>_xlfn.IFS('Local Students'!I15="P",5,'Local Students'!I15="O",3,'Local Students'!I15="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <f>_xlfn.IFS('Local Students'!J15="P",5,'Local Students'!J15="O",3,'Local Students'!J15="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <f>_xlfn.IFS('Local Students'!K15="P",5,'Local Students'!K15="O",3,'Local Students'!K15="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <f>_xlfn.IFS('Local Students'!L15="P",5,'Local Students'!L15="O",3,'Local Students'!L15="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <f>_xlfn.IFS('Local Students'!M15="P",5,'Local Students'!M15="O",3,'Local Students'!M15="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <f>_xlfn.IFS('Local Students'!N15="P",5,'Local Students'!N15="O",3,'Local Students'!N15="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="P15">
+        <f t="shared" si="1"/>
+        <v>2.33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DB59FB8-6338-47C4-AA05-389FFAB9EEAB}">
+  <dimension ref="A1:N4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1">
+        <v>45500</v>
+      </c>
+      <c r="D1" s="1">
+        <v>45507</v>
+      </c>
+      <c r="E1" s="1">
+        <v>45514</v>
+      </c>
+      <c r="F1" s="1">
+        <v>45521</v>
+      </c>
+      <c r="G1" s="1">
+        <v>45528</v>
+      </c>
+      <c r="H1" s="1">
+        <v>45535</v>
+      </c>
+      <c r="I1" s="1">
+        <v>45542</v>
+      </c>
+      <c r="J1" s="1">
+        <v>45549</v>
+      </c>
+      <c r="K1" s="1">
+        <v>45565</v>
+      </c>
+      <c r="L1" s="1">
+        <v>45572</v>
+      </c>
+      <c r="M1" s="1">
+        <v>45577</v>
+      </c>
+      <c r="N1" s="1">
+        <v>45584</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2" t="s">
+        <v>21</v>
+      </c>
+      <c r="N2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M3" t="s">
+        <v>15</v>
+      </c>
+      <c r="N3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K4" t="s">
+        <v>15</v>
+      </c>
+      <c r="L4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M4" t="s">
+        <v>21</v>
+      </c>
+      <c r="N4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4B23A5D-6BF7-4C4C-A800-462C95687A00}">
+  <dimension ref="A1:P4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="8" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1">
+        <v>45500</v>
+      </c>
+      <c r="D1" s="1">
+        <v>45507</v>
+      </c>
+      <c r="E1" s="1">
+        <v>45514</v>
+      </c>
+      <c r="F1" s="1">
+        <v>45521</v>
+      </c>
+      <c r="G1" s="1">
+        <v>45528</v>
+      </c>
+      <c r="H1" s="1">
+        <v>45535</v>
+      </c>
+      <c r="I1" s="1">
+        <v>45542</v>
+      </c>
+      <c r="J1" s="1">
+        <v>45549</v>
+      </c>
+      <c r="K1" s="1">
+        <v>45565</v>
+      </c>
+      <c r="L1" s="1">
+        <v>45572</v>
+      </c>
+      <c r="M1" s="1">
+        <v>45577</v>
+      </c>
+      <c r="N1" s="1">
+        <v>45584</v>
+      </c>
+      <c r="O1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2">
+        <f>_xlfn.IFS('Outsider Students'!C2="P", 5, 'Outsider Students'!C2="O", 5,'Outsider Students'!C2="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <f>_xlfn.IFS('Outsider Students'!D2="P", 5, 'Outsider Students'!D2="O", 5,'Outsider Students'!D2="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <f>_xlfn.IFS('Outsider Students'!E2="P", 5, 'Outsider Students'!E2="O", 5,'Outsider Students'!E2="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <f>_xlfn.IFS('Outsider Students'!F2="P", 5, 'Outsider Students'!F2="O", 5,'Outsider Students'!F2="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <f>_xlfn.IFS('Outsider Students'!G2="P", 5, 'Outsider Students'!G2="O", 5,'Outsider Students'!G2="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="H2">
+        <f>_xlfn.IFS('Outsider Students'!H2="P", 5, 'Outsider Students'!H2="O", 5,'Outsider Students'!H2="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <f>_xlfn.IFS('Outsider Students'!I2="P", 5, 'Outsider Students'!I2="O", 5,'Outsider Students'!I2="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <f>_xlfn.IFS('Outsider Students'!J2="P", 5, 'Outsider Students'!J2="O", 5,'Outsider Students'!J2="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <f>_xlfn.IFS('Outsider Students'!K2="P", 5, 'Outsider Students'!K2="O", 5,'Outsider Students'!K2="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <f>_xlfn.IFS('Outsider Students'!L2="P", 5, 'Outsider Students'!L2="O", 5,'Outsider Students'!L2="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <f>_xlfn.IFS('Outsider Students'!M2="P", 5, 'Outsider Students'!M2="O", 5,'Outsider Students'!M2="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <f>_xlfn.IFS('Outsider Students'!N2="P", 5, 'Outsider Students'!N2="O", 5,'Outsider Students'!N2="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <f>SUM(C2:N2)</f>
+        <v>15</v>
+      </c>
+      <c r="P2">
+        <f>ROUND(O2*5/60, 2)</f>
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3">
+        <f>_xlfn.IFS('Outsider Students'!C3="P", 5, 'Outsider Students'!C3="O", 5,'Outsider Students'!C3="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <f>_xlfn.IFS('Outsider Students'!D3="P", 5, 'Outsider Students'!D3="O", 5,'Outsider Students'!D3="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <f>_xlfn.IFS('Outsider Students'!E3="P", 5, 'Outsider Students'!E3="O", 5,'Outsider Students'!E3="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="F3">
+        <f>_xlfn.IFS('Outsider Students'!F3="P", 5, 'Outsider Students'!F3="O", 5,'Outsider Students'!F3="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="G3">
+        <f>_xlfn.IFS('Outsider Students'!G3="P", 5, 'Outsider Students'!G3="O", 5,'Outsider Students'!G3="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="H3">
+        <f>_xlfn.IFS('Outsider Students'!H3="P", 5, 'Outsider Students'!H3="O", 5,'Outsider Students'!H3="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="I3">
+        <f>_xlfn.IFS('Outsider Students'!I3="P", 5, 'Outsider Students'!I3="O", 5,'Outsider Students'!I3="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="J3">
+        <f>_xlfn.IFS('Outsider Students'!J3="P", 5, 'Outsider Students'!J3="O", 5,'Outsider Students'!J3="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="K3">
+        <f>_xlfn.IFS('Outsider Students'!K3="P", 5, 'Outsider Students'!K3="O", 5,'Outsider Students'!K3="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="L3">
+        <f>_xlfn.IFS('Outsider Students'!L3="P", 5, 'Outsider Students'!L3="O", 5,'Outsider Students'!L3="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <f>_xlfn.IFS('Outsider Students'!M3="P", 5, 'Outsider Students'!M3="O", 5,'Outsider Students'!M3="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="N3">
+        <f>_xlfn.IFS('Outsider Students'!N3="P", 5, 'Outsider Students'!N3="O", 5,'Outsider Students'!N3="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="O3">
+        <f t="shared" ref="O3:O4" si="0">SUM(C3:N3)</f>
+        <v>55</v>
+      </c>
+      <c r="P3">
+        <f t="shared" ref="P3:P4" si="1">ROUND(O3*5/60, 2)</f>
+        <v>4.58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4">
+        <f>_xlfn.IFS('Outsider Students'!C4="P", 5, 'Outsider Students'!C4="O", 5,'Outsider Students'!C4="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <f>_xlfn.IFS('Outsider Students'!D4="P", 5, 'Outsider Students'!D4="O", 5,'Outsider Students'!D4="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="E4">
+        <f>_xlfn.IFS('Outsider Students'!E4="P", 5, 'Outsider Students'!E4="O", 5,'Outsider Students'!E4="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <f>_xlfn.IFS('Outsider Students'!F4="P", 5, 'Outsider Students'!F4="O", 5,'Outsider Students'!F4="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="G4">
+        <f>_xlfn.IFS('Outsider Students'!G4="P", 5, 'Outsider Students'!G4="O", 5,'Outsider Students'!G4="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="H4">
+        <f>_xlfn.IFS('Outsider Students'!H4="P", 5, 'Outsider Students'!H4="O", 5,'Outsider Students'!H4="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="I4">
+        <f>_xlfn.IFS('Outsider Students'!I4="P", 5, 'Outsider Students'!I4="O", 5,'Outsider Students'!I4="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="J4">
+        <f>_xlfn.IFS('Outsider Students'!J4="P", 5, 'Outsider Students'!J4="O", 5,'Outsider Students'!J4="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <f>_xlfn.IFS('Outsider Students'!K4="P", 5, 'Outsider Students'!K4="O", 5,'Outsider Students'!K4="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="L4">
+        <f>_xlfn.IFS('Outsider Students'!L4="P", 5, 'Outsider Students'!L4="O", 5,'Outsider Students'!L4="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <f>_xlfn.IFS('Outsider Students'!M4="P", 5, 'Outsider Students'!M4="O", 5,'Outsider Students'!M4="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <f>_xlfn.IFS('Outsider Students'!N4="P", 5, 'Outsider Students'!N4="O", 5,'Outsider Students'!N4="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="P4">
+        <f t="shared" si="1"/>
+        <v>2.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/2024AIDataScienceGNRGeneral/Attendance.xlsx
+++ b/2024AIDataScienceGNRGeneral/Attendance.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\2024AIDataScienceGNRGeneral\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D4533F5-2184-4223-8158-B23AAD79695B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{010755E7-E678-4887-B483-8612F4BD153F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="28">
   <si>
     <t>Name</t>
   </si>
@@ -431,7 +431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:O18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.21875" bestFit="1" customWidth="1"/>
@@ -443,7 +443,7 @@
     <col min="10" max="10" width="6.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -483,8 +483,11 @@
       <c r="N1" s="1">
         <v>45584</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O1" s="1">
+        <v>45591</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -527,8 +530,11 @@
       <c r="N2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -571,8 +577,11 @@
       <c r="N3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -615,8 +624,11 @@
       <c r="N4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -659,8 +671,11 @@
       <c r="N5" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -703,8 +718,11 @@
       <c r="N6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -747,8 +765,11 @@
       <c r="N7" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -791,8 +812,11 @@
       <c r="N8" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -835,8 +859,11 @@
       <c r="N9" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -879,8 +906,11 @@
       <c r="N10" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -923,8 +953,11 @@
       <c r="N11" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -967,8 +1000,11 @@
       <c r="N12" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -1011,8 +1047,11 @@
       <c r="N13" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>6</v>
       </c>
@@ -1055,8 +1094,11 @@
       <c r="N14" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>7</v>
       </c>
@@ -1099,8 +1141,11 @@
       <c r="N15" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -1143,8 +1188,11 @@
       <c r="N16" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>14</v>
       </c>
@@ -1187,8 +1235,11 @@
       <c r="N17" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -1229,6 +1280,9 @@
         <v>21</v>
       </c>
       <c r="N18" t="s">
+        <v>21</v>
+      </c>
+      <c r="O18" t="s">
         <v>21</v>
       </c>
     </row>

--- a/2024AIDataScienceGNRGeneral/Attendance.xlsx
+++ b/2024AIDataScienceGNRGeneral/Attendance.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\2024AIDataScienceGNRGeneral\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{010755E7-E678-4887-B483-8612F4BD153F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{976C348E-BFFE-4A97-9E84-E6D960171943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="28">
   <si>
     <t>Name</t>
   </si>
@@ -431,7 +431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O18"/>
+  <dimension ref="A1:P18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.21875" bestFit="1" customWidth="1"/>
@@ -443,7 +443,7 @@
     <col min="10" max="10" width="6.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -486,8 +486,11 @@
       <c r="O1" s="1">
         <v>45591</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P1" s="1">
+        <v>45605</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -533,8 +536,11 @@
       <c r="O2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -580,8 +586,11 @@
       <c r="O3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -627,8 +636,11 @@
       <c r="O4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -674,8 +686,11 @@
       <c r="O5" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -721,8 +736,11 @@
       <c r="O6" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -768,8 +786,11 @@
       <c r="O7" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -815,8 +836,11 @@
       <c r="O8" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -862,8 +886,11 @@
       <c r="O9" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -909,8 +936,11 @@
       <c r="O10" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -956,8 +986,11 @@
       <c r="O11" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -1003,8 +1036,11 @@
       <c r="O12" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -1050,8 +1086,11 @@
       <c r="O13" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>6</v>
       </c>
@@ -1097,8 +1136,11 @@
       <c r="O14" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>7</v>
       </c>
@@ -1144,8 +1186,11 @@
       <c r="O15" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -1191,8 +1236,11 @@
       <c r="O16" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>14</v>
       </c>
@@ -1238,8 +1286,11 @@
       <c r="O17" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -1284,6 +1335,9 @@
       </c>
       <c r="O18" t="s">
         <v>21</v>
+      </c>
+      <c r="P18" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/2024AIDataScienceGNRGeneral/Attendance.xlsx
+++ b/2024AIDataScienceGNRGeneral/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\2024AIDataScienceGNRGeneral\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{976C348E-BFFE-4A97-9E84-E6D960171943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9F6E350-BEE5-4850-A846-29E0E7F853EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="28">
   <si>
     <t>Name</t>
   </si>
@@ -431,7 +431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P18"/>
+  <dimension ref="A1:Q18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.21875" bestFit="1" customWidth="1"/>
@@ -443,7 +443,7 @@
     <col min="10" max="10" width="6.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -489,8 +489,11 @@
       <c r="P1" s="1">
         <v>45605</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q1" s="1">
+        <v>45612</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -539,8 +542,11 @@
       <c r="P2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -589,8 +595,11 @@
       <c r="P3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -639,8 +648,11 @@
       <c r="P4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -689,8 +701,11 @@
       <c r="P5" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -739,8 +754,11 @@
       <c r="P6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -789,8 +807,11 @@
       <c r="P7" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -839,8 +860,11 @@
       <c r="P8" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -889,8 +913,11 @@
       <c r="P9" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -939,8 +966,11 @@
       <c r="P10" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -989,8 +1019,11 @@
       <c r="P11" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -1039,8 +1072,11 @@
       <c r="P12" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -1089,8 +1125,11 @@
       <c r="P13" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>6</v>
       </c>
@@ -1139,8 +1178,11 @@
       <c r="P14" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>7</v>
       </c>
@@ -1189,8 +1231,11 @@
       <c r="P15" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -1239,8 +1284,11 @@
       <c r="P16" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>14</v>
       </c>
@@ -1289,8 +1337,11 @@
       <c r="P17" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -1337,6 +1388,9 @@
         <v>21</v>
       </c>
       <c r="P18" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q18" t="s">
         <v>15</v>
       </c>
     </row>

--- a/2024AIDataScienceGNRGeneral/Attendance.xlsx
+++ b/2024AIDataScienceGNRGeneral/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\2024AIDataScienceGNRGeneral\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9F6E350-BEE5-4850-A846-29E0E7F853EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9965C5FD-E3B0-4689-AAF5-AB449B81032D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="28">
   <si>
     <t>Name</t>
   </si>
@@ -431,7 +431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q18"/>
+  <dimension ref="A1:R18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.21875" bestFit="1" customWidth="1"/>
@@ -443,7 +443,7 @@
     <col min="10" max="10" width="6.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -492,8 +492,11 @@
       <c r="Q1" s="1">
         <v>45612</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R1" s="1">
+        <v>45619</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -545,8 +548,11 @@
       <c r="Q2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -598,8 +604,11 @@
       <c r="Q3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -651,8 +660,11 @@
       <c r="Q4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -704,8 +716,11 @@
       <c r="Q5" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -757,8 +772,11 @@
       <c r="Q6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -810,8 +828,11 @@
       <c r="Q7" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -863,8 +884,11 @@
       <c r="Q8" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -916,8 +940,11 @@
       <c r="Q9" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -969,8 +996,11 @@
       <c r="Q10" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -1022,8 +1052,11 @@
       <c r="Q11" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -1075,8 +1108,11 @@
       <c r="Q12" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -1128,8 +1164,11 @@
       <c r="Q13" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>6</v>
       </c>
@@ -1181,8 +1220,11 @@
       <c r="Q14" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>7</v>
       </c>
@@ -1234,8 +1276,11 @@
       <c r="Q15" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -1287,8 +1332,11 @@
       <c r="Q16" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>14</v>
       </c>
@@ -1340,8 +1388,11 @@
       <c r="Q17" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -1391,6 +1442,9 @@
         <v>15</v>
       </c>
       <c r="Q18" t="s">
+        <v>15</v>
+      </c>
+      <c r="R18" t="s">
         <v>15</v>
       </c>
     </row>

--- a/2024AIDataScienceGNRGeneral/Attendance.xlsx
+++ b/2024AIDataScienceGNRGeneral/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\2024AIDataScienceGNRGeneral\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9965C5FD-E3B0-4689-AAF5-AB449B81032D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66E0E27E-1082-4B6E-B5EA-CD22F42FC4C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="28">
   <si>
     <t>Name</t>
   </si>
@@ -431,7 +431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R18"/>
+  <dimension ref="A1:S18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.21875" bestFit="1" customWidth="1"/>
@@ -443,7 +443,7 @@
     <col min="10" max="10" width="6.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -495,8 +495,11 @@
       <c r="R1" s="1">
         <v>45619</v>
       </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S1" s="1">
+        <v>45626</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -551,8 +554,11 @@
       <c r="R2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -607,8 +613,11 @@
       <c r="R3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -663,8 +672,11 @@
       <c r="R4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -719,8 +731,11 @@
       <c r="R5" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -775,8 +790,11 @@
       <c r="R6" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -831,8 +849,11 @@
       <c r="R7" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -887,8 +908,11 @@
       <c r="R8" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -943,8 +967,11 @@
       <c r="R9" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -999,8 +1026,11 @@
       <c r="R10" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -1055,8 +1085,11 @@
       <c r="R11" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -1111,8 +1144,11 @@
       <c r="R12" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -1167,8 +1203,11 @@
       <c r="R13" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>6</v>
       </c>
@@ -1223,8 +1262,11 @@
       <c r="R14" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>7</v>
       </c>
@@ -1279,8 +1321,11 @@
       <c r="R15" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -1335,8 +1380,11 @@
       <c r="R16" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>14</v>
       </c>
@@ -1391,8 +1439,11 @@
       <c r="R17" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -1446,6 +1497,9 @@
       </c>
       <c r="R18" t="s">
         <v>15</v>
+      </c>
+      <c r="S18" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/2024AIDataScienceGNRGeneral/Attendance.xlsx
+++ b/2024AIDataScienceGNRGeneral/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\2024AIDataScienceGNRGeneral\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66E0E27E-1082-4B6E-B5EA-CD22F42FC4C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C04D0161-E1BC-4BC8-AA2B-8B605CB575D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="28">
   <si>
     <t>Name</t>
   </si>
@@ -431,7 +431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S18"/>
+  <dimension ref="A1:T18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.21875" bestFit="1" customWidth="1"/>
@@ -443,7 +443,7 @@
     <col min="10" max="10" width="6.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -498,8 +498,11 @@
       <c r="S1" s="1">
         <v>45626</v>
       </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T1" s="1">
+        <v>45633</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -557,8 +560,11 @@
       <c r="S2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -616,8 +622,11 @@
       <c r="S3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -675,8 +684,11 @@
       <c r="S4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -734,8 +746,11 @@
       <c r="S5" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -793,8 +808,11 @@
       <c r="S6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -852,8 +870,11 @@
       <c r="S7" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -911,8 +932,11 @@
       <c r="S8" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -920,58 +944,61 @@
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E9" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G9" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="H9" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I9" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J9" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K9" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="L9" t="s">
         <v>21</v>
       </c>
       <c r="M9" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="N9" t="s">
         <v>9</v>
       </c>
       <c r="O9" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="P9" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Q9" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="R9" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="S9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+      <c r="T9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -1029,8 +1056,11 @@
       <c r="S10" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -1088,8 +1118,11 @@
       <c r="S11" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -1147,8 +1180,11 @@
       <c r="S12" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -1206,8 +1242,11 @@
       <c r="S13" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>6</v>
       </c>
@@ -1265,8 +1304,11 @@
       <c r="S14" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>7</v>
       </c>
@@ -1324,8 +1366,11 @@
       <c r="S15" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -1383,8 +1428,11 @@
       <c r="S16" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>14</v>
       </c>
@@ -1442,8 +1490,11 @@
       <c r="S17" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -1500,6 +1551,9 @@
       </c>
       <c r="S18" t="s">
         <v>21</v>
+      </c>
+      <c r="T18" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/2024AIDataScienceGNRGeneral/Attendance.xlsx
+++ b/2024AIDataScienceGNRGeneral/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\2024AIDataScienceGNRGeneral\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C04D0161-E1BC-4BC8-AA2B-8B605CB575D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E19856C6-D6A1-472E-A853-1DA9B99D9D2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="28">
   <si>
     <t>Name</t>
   </si>
@@ -431,7 +431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T18"/>
+  <dimension ref="A1:U18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.21875" bestFit="1" customWidth="1"/>
@@ -443,7 +443,7 @@
     <col min="10" max="10" width="6.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -501,8 +501,11 @@
       <c r="T1" s="1">
         <v>45633</v>
       </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U1" s="1">
+        <v>45640</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -563,8 +566,11 @@
       <c r="T2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -625,8 +631,11 @@
       <c r="T3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -687,8 +696,11 @@
       <c r="T4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -749,8 +761,11 @@
       <c r="T5" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -811,8 +826,11 @@
       <c r="T6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -873,8 +891,11 @@
       <c r="T7" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -935,8 +956,11 @@
       <c r="T8" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -997,8 +1021,11 @@
       <c r="T9" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -1059,8 +1086,11 @@
       <c r="T10" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -1121,8 +1151,11 @@
       <c r="T11" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -1183,8 +1216,11 @@
       <c r="T12" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -1245,8 +1281,11 @@
       <c r="T13" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>6</v>
       </c>
@@ -1307,8 +1346,11 @@
       <c r="T14" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>7</v>
       </c>
@@ -1369,8 +1411,11 @@
       <c r="T15" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -1431,8 +1476,11 @@
       <c r="T16" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>14</v>
       </c>
@@ -1493,8 +1541,11 @@
       <c r="T17" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -1553,6 +1604,9 @@
         <v>21</v>
       </c>
       <c r="T18" t="s">
+        <v>15</v>
+      </c>
+      <c r="U18" t="s">
         <v>15</v>
       </c>
     </row>

--- a/2024AIDataScienceGNRGeneral/Attendance.xlsx
+++ b/2024AIDataScienceGNRGeneral/Attendance.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\2024AIDataScienceGNRGeneral\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E19856C6-D6A1-472E-A853-1DA9B99D9D2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E9C40D9-10FB-42F9-BCB4-0D454E1E3C6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="28">
   <si>
     <t>Name</t>
   </si>
@@ -431,7 +431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U18"/>
+  <dimension ref="A1:V18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.21875" bestFit="1" customWidth="1"/>
@@ -443,7 +443,7 @@
     <col min="10" max="10" width="6.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -504,8 +504,11 @@
       <c r="U1" s="1">
         <v>45640</v>
       </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V1" s="1">
+        <v>45647</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -569,8 +572,11 @@
       <c r="U2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -634,8 +640,11 @@
       <c r="U3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -699,8 +708,11 @@
       <c r="U4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -764,8 +776,11 @@
       <c r="U5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -829,8 +844,11 @@
       <c r="U6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -894,8 +912,11 @@
       <c r="U7" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -959,8 +980,11 @@
       <c r="U8" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -1024,8 +1048,11 @@
       <c r="U9" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -1089,8 +1116,11 @@
       <c r="U10" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -1154,8 +1184,11 @@
       <c r="U11" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -1219,8 +1252,11 @@
       <c r="U12" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -1284,8 +1320,11 @@
       <c r="U13" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>6</v>
       </c>
@@ -1349,8 +1388,11 @@
       <c r="U14" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>7</v>
       </c>
@@ -1414,8 +1456,11 @@
       <c r="U15" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -1479,8 +1524,11 @@
       <c r="U16" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>14</v>
       </c>
@@ -1544,8 +1592,11 @@
       <c r="U17" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -1607,6 +1658,9 @@
         <v>15</v>
       </c>
       <c r="U18" t="s">
+        <v>15</v>
+      </c>
+      <c r="V18" t="s">
         <v>15</v>
       </c>
     </row>

--- a/2024AIDataScienceGNRGeneral/Attendance.xlsx
+++ b/2024AIDataScienceGNRGeneral/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\2024AIDataScienceGNRGeneral\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E9C40D9-10FB-42F9-BCB4-0D454E1E3C6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EDB13AF-86CC-4DF1-A0E4-3B4E953ACE35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="689" uniqueCount="28">
   <si>
     <t>Name</t>
   </si>
@@ -431,19 +431,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V18"/>
+  <dimension ref="A1:X18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="8" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="8" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="15" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="19" width="7" bestFit="1" customWidth="1"/>
+    <col min="20" max="23" width="6.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -507,8 +507,14 @@
       <c r="V1" s="1">
         <v>45647</v>
       </c>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W1" s="1">
+        <v>45654</v>
+      </c>
+      <c r="X1" s="1">
+        <v>45661</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -575,8 +581,14 @@
       <c r="V2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W2" t="s">
+        <v>21</v>
+      </c>
+      <c r="X2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -643,8 +655,14 @@
       <c r="V3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W3" t="s">
+        <v>9</v>
+      </c>
+      <c r="X3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -711,8 +729,14 @@
       <c r="V4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W4" t="s">
+        <v>21</v>
+      </c>
+      <c r="X4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -779,8 +803,14 @@
       <c r="V5" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W5" t="s">
+        <v>21</v>
+      </c>
+      <c r="X5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -847,8 +877,14 @@
       <c r="V6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W6" t="s">
+        <v>9</v>
+      </c>
+      <c r="X6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -915,8 +951,14 @@
       <c r="V7" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W7" t="s">
+        <v>21</v>
+      </c>
+      <c r="X7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -983,8 +1025,14 @@
       <c r="V8" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W8" t="s">
+        <v>21</v>
+      </c>
+      <c r="X8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -1051,8 +1099,14 @@
       <c r="V9" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W9" t="s">
+        <v>9</v>
+      </c>
+      <c r="X9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -1119,8 +1173,14 @@
       <c r="V10" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W10" t="s">
+        <v>21</v>
+      </c>
+      <c r="X10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -1187,8 +1247,14 @@
       <c r="V11" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W11" t="s">
+        <v>21</v>
+      </c>
+      <c r="X11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -1255,8 +1321,14 @@
       <c r="V12" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W12" t="s">
+        <v>21</v>
+      </c>
+      <c r="X12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -1323,8 +1395,14 @@
       <c r="V13" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W13" t="s">
+        <v>21</v>
+      </c>
+      <c r="X13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>6</v>
       </c>
@@ -1391,8 +1469,14 @@
       <c r="V14" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W14" t="s">
+        <v>21</v>
+      </c>
+      <c r="X14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>7</v>
       </c>
@@ -1459,8 +1543,14 @@
       <c r="V15" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W15" t="s">
+        <v>9</v>
+      </c>
+      <c r="X15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -1527,8 +1617,14 @@
       <c r="V16" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W16" t="s">
+        <v>21</v>
+      </c>
+      <c r="X16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>14</v>
       </c>
@@ -1595,8 +1691,14 @@
       <c r="V17" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W17" t="s">
+        <v>21</v>
+      </c>
+      <c r="X17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -1661,6 +1763,12 @@
         <v>15</v>
       </c>
       <c r="V18" t="s">
+        <v>15</v>
+      </c>
+      <c r="W18" t="s">
+        <v>21</v>
+      </c>
+      <c r="X18" t="s">
         <v>15</v>
       </c>
     </row>

--- a/2024AIDataScienceGNRGeneral/Attendance.xlsx
+++ b/2024AIDataScienceGNRGeneral/Attendance.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\2024AIDataScienceGNRGeneral\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EDB13AF-86CC-4DF1-A0E4-3B4E953ACE35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17C9948E-7946-4C9D-9A3A-7686CB2F29B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="689" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="705" uniqueCount="28">
   <si>
     <t>Name</t>
   </si>
@@ -431,7 +431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X18"/>
+  <dimension ref="A1:Y18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.21875" bestFit="1" customWidth="1"/>
@@ -443,7 +443,7 @@
     <col min="20" max="23" width="6.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -513,8 +513,11 @@
       <c r="X1" s="1">
         <v>45661</v>
       </c>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y1" s="1">
+        <v>45675</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -587,8 +590,11 @@
       <c r="X2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -661,8 +667,11 @@
       <c r="X3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -735,8 +744,11 @@
       <c r="X4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -810,7 +822,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -883,8 +895,11 @@
       <c r="X6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -957,8 +972,11 @@
       <c r="X7" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1031,8 +1049,11 @@
       <c r="X8" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -1105,8 +1126,11 @@
       <c r="X9" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -1179,8 +1203,11 @@
       <c r="X10" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -1253,8 +1280,11 @@
       <c r="X11" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -1327,8 +1357,11 @@
       <c r="X12" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -1401,8 +1434,11 @@
       <c r="X13" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>6</v>
       </c>
@@ -1475,8 +1511,11 @@
       <c r="X14" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>7</v>
       </c>
@@ -1549,8 +1588,11 @@
       <c r="X15" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -1623,8 +1665,11 @@
       <c r="X16" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>14</v>
       </c>
@@ -1697,8 +1742,11 @@
       <c r="X17" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -1770,6 +1818,9 @@
       </c>
       <c r="X18" t="s">
         <v>15</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
